--- a/data/Summary cost data.xlsx
+++ b/data/Summary cost data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/stepheaneff/Documents/work/GT/costed-NAPHS/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E92DADB-8054-704E-AAA4-C7C1ADCFB6B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60468EFD-4C29-CC4C-8A18-316429D90137}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3240" yWindow="2680" windowWidth="26580" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3660" yWindow="760" windowWidth="26580" windowHeight="13180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1213" uniqueCount="180">
   <si>
     <t>country</t>
   </si>
@@ -278,16 +278,304 @@
   </si>
   <si>
     <t>page 10</t>
+  </si>
+  <si>
+    <t>Indonesia</t>
+  </si>
+  <si>
+    <t>USD (2020)</t>
+  </si>
+  <si>
+    <t>page 44</t>
+  </si>
+  <si>
+    <t>Liberia</t>
+  </si>
+  <si>
+    <t>page 17</t>
+  </si>
+  <si>
+    <t>USD (2018)</t>
+  </si>
+  <si>
+    <t>pages 17-19</t>
+  </si>
+  <si>
+    <t>page 20</t>
+  </si>
+  <si>
+    <t>Myanmar</t>
+  </si>
+  <si>
+    <t>page 49</t>
+  </si>
+  <si>
+    <t>page 46</t>
+  </si>
+  <si>
+    <t>page 74</t>
+  </si>
+  <si>
+    <t>page 78</t>
+  </si>
+  <si>
+    <t>page 83</t>
+  </si>
+  <si>
+    <t>page 93</t>
+  </si>
+  <si>
+    <t>page 99</t>
+  </si>
+  <si>
+    <t>page 105</t>
+  </si>
+  <si>
+    <t>page 108</t>
+  </si>
+  <si>
+    <t>page 113</t>
+  </si>
+  <si>
+    <t>page 117</t>
+  </si>
+  <si>
+    <t>page 121</t>
+  </si>
+  <si>
+    <t>page 124</t>
+  </si>
+  <si>
+    <t>page 127</t>
+  </si>
+  <si>
+    <t>page 131</t>
+  </si>
+  <si>
+    <t>page 138</t>
+  </si>
+  <si>
+    <t>page 150</t>
+  </si>
+  <si>
+    <t>Nigeria</t>
+  </si>
+  <si>
+    <t>Annex 1</t>
+  </si>
+  <si>
+    <t>National Legislation and Financing</t>
+  </si>
+  <si>
+    <t>IHR Coordination and National IHR Focal Point Functions</t>
+  </si>
+  <si>
+    <t>Antimicrobial Resistance (AMR)</t>
+  </si>
+  <si>
+    <t>Zoonotic events and the human–animal interface</t>
+  </si>
+  <si>
+    <t>Surveillance</t>
+  </si>
+  <si>
+    <t>Linking Public Health and Security Authorities</t>
+  </si>
+  <si>
+    <t>Emergency Response Operations</t>
+  </si>
+  <si>
+    <t>Medical Countermeasures and Personnel Deployment</t>
+  </si>
+  <si>
+    <t>Risk Communication</t>
+  </si>
+  <si>
+    <t>Human Resources/Workforce Development</t>
+  </si>
+  <si>
+    <t>Sierra Leone</t>
+  </si>
+  <si>
+    <t>R.4 Medical Countermeasures and Personnel Deployment</t>
+  </si>
+  <si>
+    <t>page 43</t>
+  </si>
+  <si>
+    <t>South Sudan</t>
+  </si>
+  <si>
+    <t>Section: Cost Estimates for the NAPHS</t>
+  </si>
+  <si>
+    <t>Sri Lanka</t>
+  </si>
+  <si>
+    <t>page 16</t>
+  </si>
+  <si>
+    <t>LKR (2019)</t>
+  </si>
+  <si>
+    <t>National Legislation, Policy and Financing</t>
+  </si>
+  <si>
+    <t>IHR Coordination, Communication and Advocacy</t>
+  </si>
+  <si>
+    <t>Antimicrobial resistance</t>
+  </si>
+  <si>
+    <t>Food Safety</t>
+  </si>
+  <si>
+    <t>Zoonotic Disease</t>
+  </si>
+  <si>
+    <t>Immunizations</t>
+  </si>
+  <si>
+    <t>Biosafety and Biosecurity</t>
+  </si>
+  <si>
+    <t>Workforce Development</t>
+  </si>
+  <si>
+    <t>Emergency response operation</t>
+  </si>
+  <si>
+    <t>Medical Counter measures and Personnel Deployment</t>
+  </si>
+  <si>
+    <t>Radiation Emergencies</t>
+  </si>
+  <si>
+    <t>Tanzania</t>
+  </si>
+  <si>
+    <t>page 34, scenario A (inclusive of vaccines)</t>
+  </si>
+  <si>
+    <t>Timor-Leste</t>
+  </si>
+  <si>
+    <t>IHR Coordination Communication and Advocacy</t>
+  </si>
+  <si>
+    <t>page 21</t>
+  </si>
+  <si>
+    <t>Anti-Microbial Resistance</t>
+  </si>
+  <si>
+    <t>Medical Countermeasures and Personnel Deploymen</t>
+  </si>
+  <si>
+    <t>page 23</t>
+  </si>
+  <si>
+    <t>page 28</t>
+  </si>
+  <si>
+    <t>page 30</t>
+  </si>
+  <si>
+    <t>page 34</t>
+  </si>
+  <si>
+    <t>page 36</t>
+  </si>
+  <si>
+    <t>page 42</t>
+  </si>
+  <si>
+    <t>page 38</t>
+  </si>
+  <si>
+    <t>page 47</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>page 50</t>
+  </si>
+  <si>
+    <t>page 52</t>
+  </si>
+  <si>
+    <t>Emergency Preparedness</t>
+  </si>
+  <si>
+    <t>page 55</t>
+  </si>
+  <si>
+    <t>page 63</t>
+  </si>
+  <si>
+    <t>page 68</t>
+  </si>
+  <si>
+    <t>page 70</t>
+  </si>
+  <si>
+    <t>page 72</t>
+  </si>
+  <si>
+    <t>Uganda</t>
+  </si>
+  <si>
+    <t>page 24</t>
+  </si>
+  <si>
+    <t>page 85</t>
+  </si>
+  <si>
+    <t>UGX (2019)</t>
+  </si>
+  <si>
+    <t>page 27</t>
+  </si>
+  <si>
+    <t>page 33</t>
+  </si>
+  <si>
+    <t>page 39</t>
+  </si>
+  <si>
+    <t>page 48</t>
+  </si>
+  <si>
+    <t>page 71</t>
+  </si>
+  <si>
+    <t>page 75</t>
+  </si>
+  <si>
+    <t>page 77</t>
+  </si>
+  <si>
+    <t>page 80</t>
+  </si>
+  <si>
+    <t>page 84</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +601,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,7 +919,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H388"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" style="1" customWidth="1"/>
@@ -1939,6 +2233,9 @@
       <c r="F57" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="G57" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
@@ -1956,6 +2253,9 @@
       <c r="F58" s="1" t="s">
         <v>80</v>
       </c>
+      <c r="G58" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
@@ -1973,6 +2273,9 @@
       <c r="F59" s="1">
         <v>2349268</v>
       </c>
+      <c r="G59" s="1" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
@@ -1990,6 +2293,9 @@
       <c r="F60" s="1">
         <v>5492547</v>
       </c>
+      <c r="G60" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="H60" s="1" t="s">
         <v>84</v>
       </c>
@@ -2010,6 +2316,9 @@
       <c r="F61" s="1">
         <v>53695733</v>
       </c>
+      <c r="G61" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="H61" s="1" t="s">
         <v>85</v>
       </c>
@@ -2018,533 +2327,4897 @@
       <c r="A62" s="1">
         <v>61</v>
       </c>
+      <c r="B62" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F62" s="2">
+        <v>308462389</v>
+      </c>
+      <c r="G62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H62" s="1" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>62</v>
       </c>
+      <c r="B63" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F63" s="2">
+        <v>154392676</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="1">
         <v>63</v>
       </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B64" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F64" s="2">
+        <v>142700</v>
+      </c>
+      <c r="G64" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="1">
         <v>64</v>
       </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B65" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F65" s="2">
+        <v>4510088</v>
+      </c>
+      <c r="G65" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="1">
         <v>65</v>
       </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B66" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F66" s="2">
+        <v>2350245</v>
+      </c>
+      <c r="G66" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="1">
         <v>66</v>
       </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B67" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F67" s="2">
+        <v>6532750</v>
+      </c>
+      <c r="G67" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="1">
         <v>67</v>
       </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B68" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F68" s="2">
+        <v>6836485</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="1">
         <v>68</v>
       </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B69" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F69" s="2">
+        <v>363950</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H69" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1">
         <v>69</v>
       </c>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B70" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F70" s="2">
+        <v>4035625</v>
+      </c>
+      <c r="G70" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H70" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="1">
         <v>70</v>
       </c>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B71" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F71" s="2">
+        <v>25522515</v>
+      </c>
+      <c r="G71" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="1">
         <v>71</v>
       </c>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B72" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F72" s="2">
+        <v>34678870</v>
+      </c>
+      <c r="G72" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H72" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="1">
         <v>72</v>
       </c>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B73" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F73" s="2">
+        <v>958700</v>
+      </c>
+      <c r="G73" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="1">
         <v>73</v>
       </c>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B74" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C74" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F74" s="2">
+        <v>39948620</v>
+      </c>
+      <c r="G74" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="1">
         <v>74</v>
       </c>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B75" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C75" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F75" s="2">
+        <v>8848123</v>
+      </c>
+      <c r="G75" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H75" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B76" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F76" s="2">
+        <v>1328140</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H76" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="1">
         <v>76</v>
       </c>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B77" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C77" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F77" s="2">
+        <v>5751850</v>
+      </c>
+      <c r="G77" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H77" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="1">
         <v>77</v>
       </c>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B78" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F78" s="2">
+        <v>704080</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="1">
         <v>78</v>
       </c>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B79" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F79" s="2">
+        <v>4509051</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="1">
         <v>79</v>
       </c>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B80" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F80" s="2">
+        <v>1517095</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="1">
         <v>80</v>
       </c>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B81" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F81" s="2">
+        <v>3458965</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="1">
         <v>81</v>
       </c>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B82" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F82" s="2">
+        <v>2394825</v>
+      </c>
+      <c r="G82" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H82" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="1">
         <v>82</v>
       </c>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B83" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F83" s="2">
+        <v>158524934</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1">
         <v>83</v>
       </c>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B84" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F84" s="3">
+        <v>254347.31</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="1">
         <v>84</v>
       </c>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B85" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C85" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D85" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F85" s="2">
+        <v>491528.85</v>
+      </c>
+      <c r="G85" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H85" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="1">
         <v>85</v>
       </c>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B86" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C86" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F86" s="2">
+        <v>5399801.4699999997</v>
+      </c>
+      <c r="G86" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H86" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="1">
         <v>86</v>
       </c>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B87" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F87" s="2">
+        <v>20652080.449999999</v>
+      </c>
+      <c r="G87" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="1">
         <v>87</v>
       </c>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B88" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F88" s="3">
+        <v>343208.4</v>
+      </c>
+      <c r="G88" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H88" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="1">
         <v>88</v>
       </c>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B89" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F89" s="3">
+        <v>15011529.810000001</v>
+      </c>
+      <c r="G89" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H89" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1">
         <v>89</v>
       </c>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B90" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C90" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F90" s="2">
+        <v>46746771.740000002</v>
+      </c>
+      <c r="G90" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H90" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1">
         <v>90</v>
       </c>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B91" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C91" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F91" s="3">
+        <v>32333141.93</v>
+      </c>
+      <c r="G91" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1">
         <v>91</v>
       </c>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B92" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C92" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F92" s="3">
+        <v>2575316.6</v>
+      </c>
+      <c r="G92" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H92" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="1">
         <v>92</v>
       </c>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B93" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C93" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F93" s="2">
+        <v>181497.88</v>
+      </c>
+      <c r="G93" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H93" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1">
         <v>93</v>
       </c>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B94" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F94" s="2">
+        <v>3505474.36</v>
+      </c>
+      <c r="G94" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H94" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1">
         <v>94</v>
       </c>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B95" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C95" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F95" s="2">
+        <v>498907.05</v>
+      </c>
+      <c r="G95" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1">
         <v>95</v>
       </c>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B96" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C96" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F96" s="2">
+        <v>1121472.23</v>
+      </c>
+      <c r="G96" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H96" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1">
         <v>96</v>
       </c>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B97" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C97" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D97" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F97" s="3">
+        <v>83019.23</v>
+      </c>
+      <c r="G97" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="1">
         <v>97</v>
       </c>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B98" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C98" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F98" s="3">
+        <v>475046.67</v>
+      </c>
+      <c r="G98" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H98" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="1">
         <v>98</v>
       </c>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B99" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C99" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F99" s="3">
+        <v>242627.18</v>
+      </c>
+      <c r="G99" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H99" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="1">
         <v>99</v>
       </c>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B100" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C100" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F100" s="3">
+        <v>3692639.83</v>
+      </c>
+      <c r="G100" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H100" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="1">
         <v>100</v>
       </c>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B101" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C101" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F101" s="2">
+        <v>22585312.48</v>
+      </c>
+      <c r="G101" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H101" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="1">
         <v>101</v>
       </c>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B102" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D102" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F102" s="3">
+        <v>2238841.7799999998</v>
+      </c>
+      <c r="G102" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1">
         <v>102</v>
       </c>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B103" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D103" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F103" s="2">
+        <v>439123340</v>
+      </c>
+      <c r="G103" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H103" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="1">
         <v>103</v>
       </c>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B104" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C104" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F104" s="2">
+        <v>1332898</v>
+      </c>
+      <c r="G104" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="48" x14ac:dyDescent="0.2">
       <c r="A105" s="1">
         <v>104</v>
       </c>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B105" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C105" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F105" s="2">
+        <v>2374296</v>
+      </c>
+      <c r="G105" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="1">
         <v>105</v>
       </c>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B106" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C106" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F106" s="2">
+        <v>3965056</v>
+      </c>
+      <c r="G106" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A107" s="1">
         <v>106</v>
       </c>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B107" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C107" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F107" s="2">
+        <v>2184075</v>
+      </c>
+      <c r="G107" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="1">
         <v>107</v>
       </c>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B108" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C108" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F108" s="2">
+        <v>2622819</v>
+      </c>
+      <c r="G108" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H108" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="1">
         <v>108</v>
       </c>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B109" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C109" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D109" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F109" s="2">
+        <v>6507557</v>
+      </c>
+      <c r="G109" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H109" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="1">
         <v>109</v>
       </c>
-    </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B110" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C110" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D110" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F110" s="2">
+        <v>264556777</v>
+      </c>
+      <c r="G110" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H110" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="1">
         <v>110</v>
       </c>
-    </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B111" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C111" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F111" s="2">
+        <v>35310127</v>
+      </c>
+      <c r="G111" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H111" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="1">
         <v>111</v>
       </c>
-    </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B112" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C112" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F112" s="2">
+        <v>21871396</v>
+      </c>
+      <c r="G112" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H112" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="1">
         <v>112</v>
       </c>
-    </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B113" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C113" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F113" s="2">
+        <v>7384103</v>
+      </c>
+      <c r="G113" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A114" s="1">
         <v>113</v>
       </c>
-    </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B114" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C114" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F114" s="2">
+        <v>37262878</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H114" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="1">
         <v>114</v>
       </c>
-    </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B115" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C115" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" s="2">
+        <v>36972150</v>
+      </c>
+      <c r="G115" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A116" s="1">
         <v>115</v>
       </c>
-    </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B116" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C116" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="F116" s="2">
+        <v>571606</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="1">
         <v>116</v>
       </c>
-    </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B117" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C117" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D117" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F117" s="2">
+        <v>6900995</v>
+      </c>
+      <c r="G117" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="1">
         <v>117</v>
       </c>
-    </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B118" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C118" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D118" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F118" s="2">
+        <v>606221</v>
+      </c>
+      <c r="G118" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="1">
         <v>118</v>
       </c>
-    </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B119" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C119" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F119" s="2">
+        <v>1711218</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1">
         <v>119</v>
       </c>
-    </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B120" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C120" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F120" s="2">
+        <v>4277156</v>
+      </c>
+      <c r="G120" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="1">
         <v>120</v>
       </c>
-    </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B121" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C121" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F121" s="2">
+        <v>2049957</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="1">
         <v>121</v>
       </c>
-    </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B122" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C122" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F122" s="2">
+        <v>662055</v>
+      </c>
+      <c r="G122" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H122" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="1">
         <v>122</v>
       </c>
-    </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B123" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C123" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D123" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F123" s="2">
+        <v>291130326</v>
+      </c>
+      <c r="G123" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="1">
         <v>123</v>
       </c>
-    </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B124" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C124" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="F124" s="2">
+        <v>210735</v>
+      </c>
+      <c r="G124" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="1">
         <v>124</v>
       </c>
-    </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B125" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C125" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D125" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F125" s="2">
+        <v>2074103</v>
+      </c>
+      <c r="G125" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H125" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="1">
         <v>125</v>
       </c>
-    </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B126" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C126" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D126" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F126" s="2">
+        <v>13615857</v>
+      </c>
+      <c r="G126" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H126" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="1">
         <v>126</v>
       </c>
-    </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B127" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C127" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D127" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F127" s="2">
+        <v>13674069</v>
+      </c>
+      <c r="G127" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H127" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="1">
         <v>127</v>
       </c>
-    </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B128" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C128" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F128" s="2">
+        <v>2782264</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H128" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="1">
         <v>128</v>
       </c>
-    </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B129" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C129" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D129" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F129" s="2">
+        <v>2909178</v>
+      </c>
+      <c r="G129" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H129" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="1">
         <v>129</v>
       </c>
-    </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B130" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C130" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D130" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F130" s="2">
+        <v>54136709</v>
+      </c>
+      <c r="G130" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H130" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="1">
         <v>130</v>
       </c>
-    </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B131" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C131" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D131" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="F131" s="2">
+        <v>11824545</v>
+      </c>
+      <c r="G131" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H131" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="1">
         <v>131</v>
       </c>
-    </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B132" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C132" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="F132" s="2">
+        <v>141708348</v>
+      </c>
+      <c r="G132" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H132" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="1">
         <v>132</v>
       </c>
-    </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B133" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C133" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F133" s="2">
+        <v>194308</v>
+      </c>
+      <c r="G133" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H133" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="1">
         <v>133</v>
       </c>
-    </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B134" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C134" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D134" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F134" s="2">
+        <v>1867037</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H134" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="1">
         <v>134</v>
       </c>
-    </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B135" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C135" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D135" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="F135" s="2">
+        <v>972981</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="1">
         <v>135</v>
       </c>
-    </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B136" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C136" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D136" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F136" s="2">
+        <v>6251366</v>
+      </c>
+      <c r="G136" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H136" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="1">
         <v>136</v>
       </c>
-    </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B137" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C137" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F137" s="2">
+        <v>359687</v>
+      </c>
+      <c r="G137" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H137" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="1">
         <v>137</v>
       </c>
-    </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B138" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C138" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F138" s="2">
+        <v>174708</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="1">
         <v>138</v>
       </c>
-    </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B139" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C139" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F139" s="2">
+        <v>2829652</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H139" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="1">
         <v>139</v>
       </c>
-    </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B140" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C140" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F140" s="2">
+        <v>6211824</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H140" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="1">
         <v>140</v>
       </c>
-    </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B141" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C141" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D141" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F141" s="2">
+        <v>23911675</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H141" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="1">
         <v>141</v>
       </c>
-    </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B142" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C142" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D142" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F142" s="2">
+        <v>5421278</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="H142" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="1">
         <v>142</v>
       </c>
-    </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B143" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C143" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D143" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F143" s="2">
+        <v>69067059</v>
+      </c>
+      <c r="G143" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H143" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="1">
         <v>143</v>
       </c>
-    </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B144" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C144" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D144" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F144" s="2">
+        <v>1473169</v>
+      </c>
+      <c r="G144" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H144" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="1">
         <v>144</v>
       </c>
-    </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B145" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C145" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D145" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F145" s="2">
+        <v>625967</v>
+      </c>
+      <c r="G145" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="1">
         <v>145</v>
       </c>
-    </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B146" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C146" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F146" s="2">
+        <v>1922152</v>
+      </c>
+      <c r="G146" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H146" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="1">
         <v>146</v>
       </c>
-    </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B147" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C147" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F147" s="2">
+        <v>1468086</v>
+      </c>
+      <c r="G147" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H147" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="1">
         <v>147</v>
       </c>
-    </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B148" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C148" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D148" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F148" s="2">
+        <v>613709</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H148" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="1">
         <v>148</v>
       </c>
-    </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B149" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C149" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F149" s="2">
+        <v>1518082</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H149" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="1">
         <v>149</v>
       </c>
-    </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B150" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C150" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D150" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F150" s="2">
+        <v>36961929</v>
+      </c>
+      <c r="G150" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H150" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="1">
         <v>150</v>
       </c>
-    </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B151" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C151" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D151" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F151" s="2">
+        <v>6327276</v>
+      </c>
+      <c r="G151" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H151" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="1">
         <v>151</v>
       </c>
-    </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B152" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C152" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D152" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F152" s="2">
+        <v>3907102</v>
+      </c>
+      <c r="G152" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H152" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="1">
         <v>152</v>
       </c>
-    </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B153" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C153" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F153" s="2">
+        <v>1116072</v>
+      </c>
+      <c r="G153" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H153" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="1">
         <v>153</v>
       </c>
-    </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B154" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C154" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F154" s="2">
+        <v>118398</v>
+      </c>
+      <c r="G154" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H154" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="1">
         <v>154</v>
       </c>
-    </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B155" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C155" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D155" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F155" s="2">
+        <v>614431</v>
+      </c>
+      <c r="G155" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H155" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="1">
         <v>155</v>
       </c>
-    </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B156" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F156" s="2">
+        <v>5908071</v>
+      </c>
+      <c r="G156" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H156" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="1">
         <v>156</v>
       </c>
-    </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B157" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F157" s="2">
+        <v>179101</v>
+      </c>
+      <c r="G157" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H157" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="1">
         <v>157</v>
       </c>
-    </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B158" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C158" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D158" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F158" s="2">
+        <v>257494</v>
+      </c>
+      <c r="G158" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H158" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="1">
         <v>158</v>
       </c>
-    </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B159" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C159" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D159" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F159" s="2">
+        <v>3078049</v>
+      </c>
+      <c r="G159" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H159" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="1">
         <v>159</v>
       </c>
-    </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B160" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C160" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D160" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F160" s="2">
+        <v>2544366</v>
+      </c>
+      <c r="G160" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H160" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="1">
         <v>160</v>
       </c>
-    </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B161" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D161" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F161" s="2">
+        <v>379085</v>
+      </c>
+      <c r="G161" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H161" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="1">
         <v>161</v>
       </c>
-    </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B162" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="C162" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D162" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F162" s="2">
+        <v>54520</v>
+      </c>
+      <c r="G162" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H162" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="1">
         <v>162</v>
       </c>
-    </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B163" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C163" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F163" s="2">
+        <v>3807115500</v>
+      </c>
+      <c r="G163" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H163" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="1">
         <v>163</v>
       </c>
-    </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B164" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C164" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F164" s="2">
+        <v>1950000</v>
+      </c>
+      <c r="G164" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H164" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="1">
         <v>164</v>
       </c>
-    </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B165" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D165" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F165" s="2">
+        <v>1600000</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H165" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="1">
         <v>165</v>
       </c>
-    </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="B166" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C166" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F166" s="2">
+        <v>90000000</v>
+      </c>
+      <c r="G166" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H166" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="1">
         <v>166</v>
       </c>
+      <c r="B167" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C167" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F167" s="2">
+        <v>637700000</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H167" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A168" s="1">
+        <v>167</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C168" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F168" s="2">
+        <v>1273100000</v>
+      </c>
+      <c r="G168" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H168" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A169" s="1">
+        <v>168</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C169" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F169" s="2">
+        <v>174420000</v>
+      </c>
+      <c r="G169" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H169" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A170" s="1">
+        <v>169</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C170" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="F170" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G170" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H170" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A171" s="1">
+        <v>170</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F171" s="2">
+        <v>147000000</v>
+      </c>
+      <c r="G171" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H171" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A172" s="1">
+        <v>171</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C172" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F172" s="2">
+        <v>40000000</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H172" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A173" s="1">
+        <v>172</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C173" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F173" s="2">
+        <v>1000000</v>
+      </c>
+      <c r="G173" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H173" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A174" s="1">
+        <v>173</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C174" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F174" s="2">
+        <v>21220000</v>
+      </c>
+      <c r="G174" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H174" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A175" s="1">
+        <v>174</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F175" s="2">
+        <v>28300000</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H175" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A176" s="1">
+        <v>175</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C176" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F176" s="2">
+        <v>15700500</v>
+      </c>
+      <c r="G176" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H176" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A177" s="1">
+        <v>176</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F177" s="2">
+        <v>6000000</v>
+      </c>
+      <c r="G177" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H177" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A178" s="1">
+        <v>177</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C178" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="F178" s="2">
+        <v>125100000</v>
+      </c>
+      <c r="G178" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H178" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A179" s="1">
+        <v>178</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F179" s="2">
+        <v>6825000</v>
+      </c>
+      <c r="G179" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H179" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A180" s="1">
+        <v>179</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C180" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F180" s="2">
+        <v>179400000</v>
+      </c>
+      <c r="G180" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H180" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A181" s="1">
+        <v>180</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C181" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F181" s="2">
+        <v>1045500000</v>
+      </c>
+      <c r="G181" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H181" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A182" s="1">
+        <v>181</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F182" s="2">
+        <v>11300000</v>
+      </c>
+      <c r="G182" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="H182" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A183" s="1">
+        <v>182</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C183" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F183" s="2">
+        <v>603158558</v>
+      </c>
+      <c r="G183" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H183" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A184" s="1">
+        <v>183</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C184" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F184" s="2">
+        <v>164318</v>
+      </c>
+      <c r="G184" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H184" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A185" s="1">
+        <v>184</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F185" s="2">
+        <v>788805</v>
+      </c>
+      <c r="G185" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H185" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A186" s="1">
+        <v>185</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C186" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F186" s="2">
+        <v>3403830</v>
+      </c>
+      <c r="G186" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H186" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A187" s="1">
+        <v>190</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F187" s="2">
+        <v>4779094</v>
+      </c>
+      <c r="G187" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H187" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A188" s="1">
+        <v>191</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C188" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F188" s="2">
+        <v>1999377</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H188" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A189" s="1">
+        <v>192</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F189" s="2">
+        <v>4218107</v>
+      </c>
+      <c r="G189" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H189" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A190" s="1">
+        <v>193</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C190" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F190" s="2">
+        <v>523498273</v>
+      </c>
+      <c r="G190" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H190" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A191" s="1">
+        <v>197</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C191" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F191" s="2">
+        <v>31429402</v>
+      </c>
+      <c r="G191" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H191" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A192" s="1">
+        <v>198</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C192" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F192" s="2">
+        <v>6899134</v>
+      </c>
+      <c r="G192" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H192" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A193" s="1">
+        <v>199</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C193" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F193" s="2">
+        <v>41723</v>
+      </c>
+      <c r="G193" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H193" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A194" s="1">
+        <v>200</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C194" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F194" s="2">
+        <v>11959114</v>
+      </c>
+      <c r="G194" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H194" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A195" s="1">
+        <v>204</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C195" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D195" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F195" s="2">
+        <v>432761</v>
+      </c>
+      <c r="G195" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H195" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A196" s="1">
+        <v>205</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C196" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F196" s="2">
+        <v>2767341</v>
+      </c>
+      <c r="G196" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H196" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A197" s="1">
+        <v>206</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C197" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D197" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F197" s="2">
+        <v>297864</v>
+      </c>
+      <c r="G197" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H197" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A198" s="1">
+        <v>207</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="F198" s="2">
+        <v>373282</v>
+      </c>
+      <c r="G198" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H198" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A199" s="1">
+        <v>208</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C199" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D199" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F199" s="2">
+        <v>979534</v>
+      </c>
+      <c r="G199" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H199" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A200" s="1">
+        <v>212</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F200" s="2">
+        <v>6386634</v>
+      </c>
+      <c r="G200" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H200" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A201" s="1">
+        <v>213</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F201" s="2">
+        <v>978057</v>
+      </c>
+      <c r="G201" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H201" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A202" s="1">
+        <v>214</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F202" s="2">
+        <v>1916809</v>
+      </c>
+      <c r="G202" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H202" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A203" s="1">
+        <v>222</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C203" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D203" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F203" s="2">
+        <v>247300</v>
+      </c>
+      <c r="G203" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H203" s="1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A204" s="1">
+        <v>223</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C204" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D204" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F204" s="2">
+        <v>415110</v>
+      </c>
+      <c r="G204" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H204" s="1" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A205" s="1">
+        <v>224</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C205" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D205" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="F205" s="2">
+        <v>1054400</v>
+      </c>
+      <c r="G205" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H205" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A206" s="1">
+        <v>225</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C206" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D206" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F206" s="2">
+        <v>535275</v>
+      </c>
+      <c r="G206" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H206" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A207" s="1">
+        <v>226</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C207" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D207" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F207" s="2">
+        <v>4917340</v>
+      </c>
+      <c r="G207" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H207" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A208" s="1">
+        <v>227</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C208" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D208" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F208" s="2">
+        <v>322930</v>
+      </c>
+      <c r="G208" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H208" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A209" s="1">
+        <v>228</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C209" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D209" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F209" s="2">
+        <v>914716</v>
+      </c>
+      <c r="G209" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H209" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A210" s="1">
+        <v>229</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C210" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F210" s="2">
+        <v>3636990</v>
+      </c>
+      <c r="G210" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H210" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A211" s="1">
+        <v>230</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C211" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D211" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F211" s="2">
+        <v>1930412</v>
+      </c>
+      <c r="G211" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H211" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A212" s="1">
+        <v>231</v>
+      </c>
+      <c r="B212" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C212" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F212" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G212" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H212" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A213" s="1">
+        <v>232</v>
+      </c>
+      <c r="B213" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C213" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F213" s="2">
+        <v>520360</v>
+      </c>
+      <c r="G213" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H213" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A214" s="1">
+        <v>233</v>
+      </c>
+      <c r="B214" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C214" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="F214" s="2">
+        <v>436420</v>
+      </c>
+      <c r="G214" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H214" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A215" s="1">
+        <v>234</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C215" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F215" s="2">
+        <v>255950</v>
+      </c>
+      <c r="G215" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H215" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A216" s="1">
+        <v>235</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C216" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F216" s="2">
+        <v>36440</v>
+      </c>
+      <c r="G216" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H216" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A217" s="1">
+        <v>236</v>
+      </c>
+      <c r="B217" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C217" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D217" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F217" s="2">
+        <v>673560</v>
+      </c>
+      <c r="G217" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H217" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A218" s="1">
+        <v>237</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C218" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D218" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F218" s="2">
+        <v>462055</v>
+      </c>
+      <c r="G218" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H218" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A219" s="1">
+        <v>238</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C219" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D219" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F219" s="2">
+        <v>1271060</v>
+      </c>
+      <c r="G219" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H219" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A220" s="1">
+        <v>239</v>
+      </c>
+      <c r="B220" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C220" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D220" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F220" s="2">
+        <v>49840</v>
+      </c>
+      <c r="G220" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H220" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A221" s="1">
+        <v>240</v>
+      </c>
+      <c r="B221" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D221" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="F221" s="2">
+        <v>177310</v>
+      </c>
+      <c r="G221" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H221" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A222" s="1">
+        <v>241</v>
+      </c>
+      <c r="B222" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="C222" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D222" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F222" s="2">
+        <v>17857468</v>
+      </c>
+      <c r="G222" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="H222" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A223" s="1">
+        <v>242</v>
+      </c>
+      <c r="B223" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C223" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D223" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F223" s="2">
+        <v>2346091355</v>
+      </c>
+      <c r="G223" t="s">
+        <v>170</v>
+      </c>
+      <c r="H223" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A224" s="1">
+        <v>243</v>
+      </c>
+      <c r="B224" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C224" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D224" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F224" s="2">
+        <v>2053518805</v>
+      </c>
+      <c r="G224" t="s">
+        <v>170</v>
+      </c>
+      <c r="H224" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A225" s="1">
+        <v>244</v>
+      </c>
+      <c r="B225" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C225" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D225" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F225" s="2">
+        <v>27255662244</v>
+      </c>
+      <c r="G225" t="s">
+        <v>170</v>
+      </c>
+      <c r="H225" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A226" s="1">
+        <v>245</v>
+      </c>
+      <c r="B226" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C226" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D226" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F226" s="2">
+        <v>5195094477</v>
+      </c>
+      <c r="G226" t="s">
+        <v>170</v>
+      </c>
+      <c r="H226" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A227" s="1">
+        <v>246</v>
+      </c>
+      <c r="B227" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C227" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D227" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F227" s="2">
+        <v>10244621028</v>
+      </c>
+      <c r="G227" t="s">
+        <v>170</v>
+      </c>
+      <c r="H227" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A228" s="1">
+        <v>247</v>
+      </c>
+      <c r="B228" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C228" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D228" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="F228" s="2">
+        <v>2225685962</v>
+      </c>
+      <c r="G228" t="s">
+        <v>170</v>
+      </c>
+      <c r="H228" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A229" s="1">
+        <v>248</v>
+      </c>
+      <c r="B229" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C229" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D229" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F229" s="2">
+        <v>8887960226</v>
+      </c>
+      <c r="G229" t="s">
+        <v>170</v>
+      </c>
+      <c r="H229" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A230" s="1">
+        <v>249</v>
+      </c>
+      <c r="B230" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C230" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D230" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F230" s="2">
+        <v>13484064490</v>
+      </c>
+      <c r="G230" t="s">
+        <v>170</v>
+      </c>
+      <c r="H230" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A231" s="1">
+        <v>250</v>
+      </c>
+      <c r="B231" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C231" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D231" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F231" s="2">
+        <v>28723043437</v>
+      </c>
+      <c r="G231" t="s">
+        <v>170</v>
+      </c>
+      <c r="H231" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A232" s="1">
+        <v>251</v>
+      </c>
+      <c r="B232" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C232" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D232" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F232" s="2">
+        <v>7281805328</v>
+      </c>
+      <c r="G232" t="s">
+        <v>170</v>
+      </c>
+      <c r="H232" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A233" s="1">
+        <v>252</v>
+      </c>
+      <c r="B233" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C233" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D233" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F233" s="2">
+        <v>1464725845</v>
+      </c>
+      <c r="G233" t="s">
+        <v>170</v>
+      </c>
+      <c r="H233" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A234" s="1">
+        <v>253</v>
+      </c>
+      <c r="B234" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C234" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D234" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F234" s="2">
+        <v>1950922906</v>
+      </c>
+      <c r="G234" t="s">
+        <v>170</v>
+      </c>
+      <c r="H234" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A235" s="1">
+        <v>254</v>
+      </c>
+      <c r="B235" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C235" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D235" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="F235" s="2">
+        <v>885932730</v>
+      </c>
+      <c r="G235" t="s">
+        <v>170</v>
+      </c>
+      <c r="H235" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A236" s="1">
+        <v>255</v>
+      </c>
+      <c r="B236" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C236" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D236" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="F236" s="2">
+        <v>11068089527</v>
+      </c>
+      <c r="G236" t="s">
+        <v>170</v>
+      </c>
+      <c r="H236" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A237" s="1">
+        <v>256</v>
+      </c>
+      <c r="B237" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C237" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D237" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F237" s="2">
+        <v>14671014464</v>
+      </c>
+      <c r="G237" t="s">
+        <v>170</v>
+      </c>
+      <c r="H237" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A238" s="1">
+        <v>257</v>
+      </c>
+      <c r="B238" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C238" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D238" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="F238" s="2">
+        <v>10589643004</v>
+      </c>
+      <c r="G238" t="s">
+        <v>170</v>
+      </c>
+      <c r="H238" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A239" s="1">
+        <v>258</v>
+      </c>
+      <c r="B239" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C239" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D239" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F239" s="2">
+        <v>3252244500</v>
+      </c>
+      <c r="G239" t="s">
+        <v>170</v>
+      </c>
+      <c r="H239" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A240" s="1">
+        <v>259</v>
+      </c>
+      <c r="B240" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C240" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D240" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F240" s="2">
+        <v>4191108684</v>
+      </c>
+      <c r="G240" t="s">
+        <v>170</v>
+      </c>
+      <c r="H240" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A241" s="1">
+        <v>260</v>
+      </c>
+      <c r="B241" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C241" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D241" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F241" s="2">
+        <v>4937711997</v>
+      </c>
+      <c r="G241" t="s">
+        <v>170</v>
+      </c>
+      <c r="H241" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A242" s="1">
+        <v>261</v>
+      </c>
+      <c r="B242" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C242" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D242" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F242" s="2">
+        <v>160708941019</v>
+      </c>
+      <c r="G242" t="s">
+        <v>170</v>
+      </c>
+      <c r="H242" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A243" s="1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A244" s="1">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A245" s="1">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A246" s="1">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A247" s="1">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A248" s="1">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A249" s="1">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A250" s="1">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A251" s="1">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A252" s="1">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A253" s="1">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A254" s="1">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A255" s="1">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A256" s="1">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A257" s="1">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A258" s="1">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A259" s="1">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A260" s="1">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A261" s="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A262" s="1">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A263" s="1">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A264" s="1">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A265" s="1">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A266" s="1">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A267" s="1">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A268" s="1">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A269" s="1">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A270" s="1">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A271" s="1">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A272" s="1">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A273" s="1">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A274" s="1">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A275" s="1">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A276" s="1">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A277" s="1">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A278" s="1">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A279" s="1">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A280" s="1">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A281" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A282" s="1">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A283" s="1">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A284" s="1">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A285" s="1">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A286" s="1">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A287" s="1">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A288" s="1">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A289" s="1">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A290" s="1">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A291" s="1">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A292" s="1">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A293" s="1">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A294" s="1">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A295" s="1">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A296" s="1">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A297" s="1">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A298" s="1">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A299" s="1">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A300" s="1">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A301" s="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A302" s="1">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A303" s="1">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A304" s="1">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A305" s="1">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A306" s="1">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A307" s="1">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A308" s="1">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A309" s="1">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A310" s="1">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A311" s="1">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A312" s="1">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A313" s="1">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A314" s="1">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A315" s="1">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A316" s="1">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A317" s="1">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A318" s="1">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A319" s="1">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A320" s="1">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A321" s="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A322" s="1">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A323" s="1">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A324" s="1">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="325" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A325" s="1">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="326" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A326" s="1">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="327" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A327" s="1">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="328" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A328" s="1">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="329" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A329" s="1">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="330" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A330" s="1">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="331" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A331" s="1">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="332" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A332" s="1">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="333" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A333" s="1">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="334" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A334" s="1">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="335" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A335" s="1">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="336" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A336" s="1">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="337" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A337" s="1">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="338" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A338" s="1">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="339" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A339" s="1">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="340" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A340" s="1">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="341" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A341" s="1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="342" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A342" s="1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="343" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A343" s="1">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="344" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A344" s="1">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="345" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A345" s="1">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="346" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A346" s="1">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="347" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A347" s="1">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="348" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A348" s="1">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="349" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A349" s="1">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="350" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A350" s="1">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="351" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A351" s="1">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="352" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A352" s="1">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="353" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A353" s="1">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="354" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A354" s="1">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="355" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A355" s="1">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="356" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A356" s="1">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="357" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A357" s="1">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="358" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A358" s="1">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="359" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A359" s="1">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="360" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A360" s="1">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="361" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A361" s="1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="362" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A362" s="1">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="363" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A363" s="1">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="364" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A364" s="1">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="365" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A365" s="1">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="366" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A366" s="1">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="367" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A367" s="1">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="368" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A368" s="1">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="369" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A369" s="1">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="370" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A370" s="1">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="371" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A371" s="1">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="372" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A372" s="1">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="373" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A373" s="1">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="374" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A374" s="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="375" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A375" s="1">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="376" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A376" s="1">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="377" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A377" s="1">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="378" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A378" s="1">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="379" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A379" s="1">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="380" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A380" s="1">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="381" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A381" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="382" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A382" s="1">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="383" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A383" s="1">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="384" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A384" s="1">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="385" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A385" s="1">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="386" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A386" s="1">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="387" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A387" s="1">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="388" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A388" s="1">
+        <v>407</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>